--- a/AAII_Financials/Quarterly/CIHKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CIHKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>CIHKY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,102 +2126,109 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66901300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2241700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49150200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2068400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46373000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1925300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43450600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2184800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43056900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2233800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46729600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1954600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35424600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1771800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35041300</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>135388900</v>
+      </c>
+      <c r="E42" s="3">
         <v>258867300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>98295400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>205830100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99859300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>223633000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>86523700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>227736500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>82902200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>147195500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>65964100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>129497000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>80398400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>138701000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>71276300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2164,308 +2256,329 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>12800600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>14904900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>76100</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>50900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>52500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>58800</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>66100</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13404900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9016900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>58606200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2912700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7865200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1124500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>59689800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>967400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12548700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>305900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6802000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>382600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>56569200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>325100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6685000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>291646600</v>
+      </c>
+      <c r="E46" s="3">
         <v>270125800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>277926900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>210811200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>219884000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>226682800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>259179600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>230888700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>209384700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>272945200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>195234200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>212105500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246659400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>240933900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>190601300</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>581917800</v>
+      </c>
+      <c r="E47" s="3">
         <v>525759100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>541335600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>482461000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>501214700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>448193900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>469523800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>410141700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>423900700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>374544600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>413960400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>359124500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>376948800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>360424500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>374657500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21659800</v>
+      </c>
+      <c r="E48" s="3">
         <v>20014100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20289500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19268200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18987700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19132000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19248400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20013800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18521900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18894100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18670300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17662500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16784200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17747500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17031800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2307300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2292000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2281000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2244600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2248400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2239800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2241400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1728000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2287900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1729700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1785800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1749900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2402100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1914500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1943000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7925700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7427700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6397500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9160400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6828600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14233600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6973700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9117800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8029600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7071800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6957500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9243200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8274300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10112500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7457700</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2029395800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1955067400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1868712500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1776052800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1766820800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1726699100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1664867700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1661524400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1592808900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1595488700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1555300900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1462052100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1480886900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1529836400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1470004100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1671499700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1604130500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1536460300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1465131100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1419248600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1402073900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1342068600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1342944000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1263403100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1259732300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1221722200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1169349600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1184319900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1223571200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1186040700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9967200</v>
+      </c>
+      <c r="E58" s="3">
         <v>20094400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27828800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22616600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19983900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20727600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38354600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10969400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17472600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24941800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>38580300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19842700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16159700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20423800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>34088900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27337200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2631700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21041800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2394700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11526700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2254900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8995400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2107300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7358400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2258600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6358400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2431100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3592000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3364400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9307500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1726612100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1634213900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1604346800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1498208900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1469473600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1432367100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1408846600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1361173300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1308219900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1290858400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1283647100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1196154900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1218360800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1250776900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1242163900</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>72560500</v>
+      </c>
+      <c r="E61" s="3">
         <v>80132700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62326100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>69638700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>84760900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>93231300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>68809400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>104976800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>103334600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>118610900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>98619900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>99335300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>95378400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>104638400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67305100</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30336800</v>
+      </c>
+      <c r="E62" s="3">
         <v>52956300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18214000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28419800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30854900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27532000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17408900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29162300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26624300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29190900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18866900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25543800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30069400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29154800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20885300</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1830170000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1767955600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1685580500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1596940500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1585791200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1553907300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1495877700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1496204700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1439094800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1439614300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1402185100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1322077400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1344942000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1385749400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1331652600</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3329,46 +3496,49 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>3927100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>3858300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>3834300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>3785300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>3763200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>3915900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>3779900</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>3804200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>3873700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>3764500</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>3787500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>3998700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>3982500</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>151531900</v>
+      </c>
+      <c r="E72" s="3">
         <v>147449300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>140049000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>136675500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>130402400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>130770900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>124900600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>125462800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>115818700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>118646800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>115442300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>108065100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>103466500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>110531900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>104452100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>198008600</v>
+      </c>
+      <c r="E76" s="3">
         <v>185918600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>178057700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>174151200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>176130700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>167951400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>164204600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>160390500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>148996800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>151166400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>147922300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>134962400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130945800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138825300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>133102600</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>1035300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>2017800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-1094900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>993000</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>319400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>609900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>451600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>547700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>593400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>617300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>614500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>376500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1919800</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26316400</v>
+      </c>
+      <c r="E89" s="3">
         <v>18245900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39363300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5853600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5504800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13095300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21891700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>25526100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>54225300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39591400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1850300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-50628400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>45446800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-34245900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3193500</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2549800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-786400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1776000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1196500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-573000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-426700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1215900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1066400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1046400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1519400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1346000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-717300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-837000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1355800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1386900</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11602600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12675800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>79900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21222600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3565400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27552300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23476000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9477900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7725600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>155000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8906200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10285200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3451600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13374900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-34902600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>182300</v>
+      </c>
+      <c r="E96" s="3">
         <v>3704000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>430200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>7408400</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>305800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>7425600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>157800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>6342000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2859500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3866700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3902000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17035800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3809400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6705000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-557200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10868500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45709000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>57422100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>35828500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>35068800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-31686500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>38806300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>60679000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>231900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-252900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>148800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>27000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-513900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>297700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>737000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-248800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-268800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>369800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>926700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-114500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-178500</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17559300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1543000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35165600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-32456000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12846500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21172200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1909600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4926800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>939500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18012600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28258600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25547100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11045700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9063400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>22314100</v>
       </c>
     </row>
